--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,6 +1157,623 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122307304</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96692</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>340549</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6395257</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122306971</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94928</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>535</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skuggmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dicranodontium denudatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>340311</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6395441</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122306231</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5193</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öst om Landvetter flygplats, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>340201</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6395464</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122307101</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96692</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>340396</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6395398</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122307224</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96692</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>340498</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6395324</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122307133</v>
+      </c>
+      <c r="B11" t="n">
+        <v>94928</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>535</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skuggmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dicranodontium denudatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>340396</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6395398</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122306971</v>
+        <v>122306231</v>
       </c>
       <c r="B7" t="n">
-        <v>94928</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,34 +1277,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>535</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340311</v>
+        <v>340201</v>
       </c>
       <c r="R7" t="n">
-        <v>6395441</v>
+        <v>6395464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122306231</v>
+        <v>122307101</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
+        <v>96692</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,39 +1384,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340201</v>
+        <v>340396</v>
       </c>
       <c r="R8" t="n">
-        <v>6395464</v>
+        <v>6395398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307101</v>
+        <v>122307224</v>
       </c>
       <c r="B9" t="n">
         <v>96692</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340396</v>
+        <v>340498</v>
       </c>
       <c r="R9" t="n">
-        <v>6395398</v>
+        <v>6395324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122307224</v>
+        <v>122307133</v>
       </c>
       <c r="B10" t="n">
-        <v>96692</v>
+        <v>94928</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,21 +1588,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340498</v>
+        <v>340396</v>
       </c>
       <c r="R10" t="n">
-        <v>6395324</v>
+        <v>6395398</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,14 +1674,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122307133</v>
+        <v>122306971</v>
       </c>
       <c r="B11" t="n">
         <v>94928</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>340396</v>
+        <v>340311</v>
       </c>
       <c r="R11" t="n">
-        <v>6395398</v>
+        <v>6395441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122307304</v>
+        <v>122306231</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,34 +1175,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340549</v>
+        <v>340201</v>
       </c>
       <c r="R6" t="n">
-        <v>6395257</v>
+        <v>6395464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122307133</v>
+        <v>122307224</v>
       </c>
       <c r="B7" t="n">
-        <v>94944</v>
+        <v>96708</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,21 +1282,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>535</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340396</v>
+        <v>340498</v>
       </c>
       <c r="R7" t="n">
-        <v>6395398</v>
+        <v>6395324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122307224</v>
+        <v>122307101</v>
       </c>
       <c r="B8" t="n">
         <v>96708</v>
@@ -1403,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340498</v>
+        <v>340396</v>
       </c>
       <c r="R8" t="n">
-        <v>6395324</v>
+        <v>6395398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307101</v>
+        <v>122307133</v>
       </c>
       <c r="B9" t="n">
-        <v>96708</v>
+        <v>94944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,21 +1486,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1567,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122306231</v>
+        <v>122307304</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>96708</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,39 +1588,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340201</v>
+        <v>340549</v>
       </c>
       <c r="R10" t="n">
-        <v>6395464</v>
+        <v>6395257</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122306231</v>
+        <v>122307304</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>96718</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,39 +1175,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340201</v>
+        <v>340549</v>
       </c>
       <c r="R6" t="n">
-        <v>6395464</v>
+        <v>6395257</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122307224</v>
+        <v>122307133</v>
       </c>
       <c r="B7" t="n">
-        <v>96708</v>
+        <v>94954</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,21 +1277,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1306,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340498</v>
+        <v>340396</v>
       </c>
       <c r="R7" t="n">
-        <v>6395324</v>
+        <v>6395398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122307101</v>
+        <v>122306231</v>
       </c>
       <c r="B8" t="n">
-        <v>96708</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,34 +1379,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340396</v>
+        <v>340201</v>
       </c>
       <c r="R8" t="n">
-        <v>6395398</v>
+        <v>6395464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307133</v>
+        <v>122307224</v>
       </c>
       <c r="B9" t="n">
-        <v>94944</v>
+        <v>96718</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>535</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340396</v>
+        <v>340498</v>
       </c>
       <c r="R9" t="n">
-        <v>6395398</v>
+        <v>6395324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122307304</v>
+        <v>122307101</v>
       </c>
       <c r="B10" t="n">
-        <v>96708</v>
+        <v>96718</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340549</v>
+        <v>340396</v>
       </c>
       <c r="R10" t="n">
-        <v>6395257</v>
+        <v>6395398</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
         <v>122306971</v>
       </c>
       <c r="B11" t="n">
-        <v>94944</v>
+        <v>94954</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122307304</v>
+        <v>122307101</v>
       </c>
       <c r="B6" t="n">
         <v>96718</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340549</v>
+        <v>340396</v>
       </c>
       <c r="R6" t="n">
-        <v>6395257</v>
+        <v>6395398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122307133</v>
+        <v>122306231</v>
       </c>
       <c r="B7" t="n">
-        <v>94954</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,34 +1277,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>535</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340396</v>
+        <v>340201</v>
       </c>
       <c r="R7" t="n">
-        <v>6395398</v>
+        <v>6395464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122306231</v>
+        <v>122307304</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
+        <v>96718</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,39 +1384,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340201</v>
+        <v>340549</v>
       </c>
       <c r="R8" t="n">
-        <v>6395464</v>
+        <v>6395257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122307101</v>
+        <v>122307133</v>
       </c>
       <c r="B10" t="n">
-        <v>96718</v>
+        <v>94954</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,21 +1588,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122307101</v>
+        <v>122307304</v>
       </c>
       <c r="B6" t="n">
-        <v>96718</v>
+        <v>96730</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340396</v>
+        <v>340549</v>
       </c>
       <c r="R6" t="n">
-        <v>6395398</v>
+        <v>6395257</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122306231</v>
+        <v>122307101</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>96730</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,39 +1277,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340201</v>
+        <v>340396</v>
       </c>
       <c r="R7" t="n">
-        <v>6395464</v>
+        <v>6395398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122307304</v>
+        <v>122307133</v>
       </c>
       <c r="B8" t="n">
-        <v>96718</v>
+        <v>94966</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,21 +1379,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340549</v>
+        <v>340396</v>
       </c>
       <c r="R8" t="n">
-        <v>6395257</v>
+        <v>6395398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307224</v>
+        <v>122306231</v>
       </c>
       <c r="B9" t="n">
-        <v>96718</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,34 +1481,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340498</v>
+        <v>340201</v>
       </c>
       <c r="R9" t="n">
-        <v>6395324</v>
+        <v>6395464</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122307133</v>
+        <v>122307224</v>
       </c>
       <c r="B10" t="n">
-        <v>94954</v>
+        <v>96730</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,21 +1588,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>535</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340396</v>
+        <v>340498</v>
       </c>
       <c r="R10" t="n">
-        <v>6395398</v>
+        <v>6395324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
         <v>122306971</v>
       </c>
       <c r="B11" t="n">
-        <v>94954</v>
+        <v>94966</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>122307304</v>
       </c>
       <c r="B6" t="n">
-        <v>96730</v>
+        <v>96735</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122307101</v>
+        <v>122307224</v>
       </c>
       <c r="B7" t="n">
-        <v>96730</v>
+        <v>96735</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340396</v>
+        <v>340498</v>
       </c>
       <c r="R7" t="n">
-        <v>6395398</v>
+        <v>6395324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
         <v>122307133</v>
       </c>
       <c r="B8" t="n">
-        <v>94966</v>
+        <v>94971</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122307224</v>
+        <v>122307101</v>
       </c>
       <c r="B10" t="n">
-        <v>96730</v>
+        <v>96735</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340498</v>
+        <v>340396</v>
       </c>
       <c r="R10" t="n">
-        <v>6395324</v>
+        <v>6395398</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
         <v>122306971</v>
       </c>
       <c r="B11" t="n">
-        <v>94966</v>
+        <v>94971</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>122307304</v>
       </c>
       <c r="B6" t="n">
-        <v>96735</v>
+        <v>96744</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,11 +1176,6 @@
       </c>
       <c r="E6" t="n">
         <v>2569</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Stor revmossa</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1261,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122307224</v>
+        <v>122307133</v>
       </c>
       <c r="B7" t="n">
-        <v>96735</v>
+        <v>94980</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,21 +1272,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Stor revmossa</t>
-        </is>
+        <v>535</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340498</v>
+        <v>340396</v>
       </c>
       <c r="R7" t="n">
-        <v>6395324</v>
+        <v>6395398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122307133</v>
+        <v>122307101</v>
       </c>
       <c r="B8" t="n">
-        <v>94971</v>
+        <v>96744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,21 +1369,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>535</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Skuggmossa</t>
-        </is>
+        <v>2569</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1483,11 +1468,6 @@
       <c r="E9" t="n">
         <v>105930</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Semanotus undatus</t>
@@ -1572,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122307101</v>
+        <v>122307224</v>
       </c>
       <c r="B10" t="n">
-        <v>96735</v>
+        <v>96744</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,11 +1570,6 @@
       <c r="E10" t="n">
         <v>2569</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Stor revmossa</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Bazzania trilobata</t>
@@ -1612,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340396</v>
+        <v>340498</v>
       </c>
       <c r="R10" t="n">
-        <v>6395398</v>
+        <v>6395324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1652,7 @@
         <v>122306971</v>
       </c>
       <c r="B11" t="n">
-        <v>94971</v>
+        <v>94980</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,11 +1666,6 @@
       </c>
       <c r="E11" t="n">
         <v>535</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Skuggmossa</t>
-        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122307304</v>
+        <v>122307101</v>
       </c>
       <c r="B6" t="n">
-        <v>96744</v>
+        <v>96757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,6 +1177,11 @@
       <c r="E6" t="n">
         <v>2569</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Bazzania trilobata</t>
@@ -1194,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340549</v>
+        <v>340396</v>
       </c>
       <c r="R6" t="n">
-        <v>6395257</v>
+        <v>6395398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122307133</v>
+        <v>122306231</v>
       </c>
       <c r="B7" t="n">
-        <v>94980</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,29 +1277,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>535</v>
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340396</v>
+        <v>340201</v>
       </c>
       <c r="R7" t="n">
-        <v>6395398</v>
+        <v>6395464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122307101</v>
+        <v>122307224</v>
       </c>
       <c r="B8" t="n">
-        <v>96744</v>
+        <v>96757</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,6 +1386,11 @@
       <c r="E8" t="n">
         <v>2569</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Bazzania trilobata</t>
@@ -1388,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340396</v>
+        <v>340498</v>
       </c>
       <c r="R8" t="n">
-        <v>6395398</v>
+        <v>6395324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122306231</v>
+        <v>122307304</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>96757</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,34 +1486,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>2569</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340201</v>
+        <v>340549</v>
       </c>
       <c r="R9" t="n">
-        <v>6395464</v>
+        <v>6395257</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122307224</v>
+        <v>122307133</v>
       </c>
       <c r="B10" t="n">
-        <v>96744</v>
+        <v>94993</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,16 +1588,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>535</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skuggmossa</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1587,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340498</v>
+        <v>340396</v>
       </c>
       <c r="R10" t="n">
-        <v>6395324</v>
+        <v>6395398</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1677,7 @@
         <v>122306971</v>
       </c>
       <c r="B11" t="n">
-        <v>94980</v>
+        <v>94993</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,6 +1691,11 @@
       </c>
       <c r="E11" t="n">
         <v>535</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skuggmossa</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122307101</v>
+        <v>122306231</v>
       </c>
       <c r="B6" t="n">
-        <v>96757</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,34 +1175,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340396</v>
+        <v>340201</v>
       </c>
       <c r="R6" t="n">
-        <v>6395398</v>
+        <v>6395464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122306231</v>
+        <v>122307304</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>96770</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,39 +1282,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340201</v>
+        <v>340549</v>
       </c>
       <c r="R7" t="n">
-        <v>6395464</v>
+        <v>6395257</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,7 +1371,7 @@
         <v>122307224</v>
       </c>
       <c r="B8" t="n">
-        <v>96757</v>
+        <v>96770</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307304</v>
+        <v>122307101</v>
       </c>
       <c r="B9" t="n">
-        <v>96757</v>
+        <v>96770</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340549</v>
+        <v>340396</v>
       </c>
       <c r="R9" t="n">
-        <v>6395257</v>
+        <v>6395398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
         <v>122307133</v>
       </c>
       <c r="B10" t="n">
-        <v>94993</v>
+        <v>95006</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>122306971</v>
       </c>
       <c r="B11" t="n">
-        <v>94993</v>
+        <v>95006</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122306231</v>
+        <v>122307224</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>96770</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,39 +1175,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340201</v>
+        <v>340498</v>
       </c>
       <c r="R6" t="n">
-        <v>6395464</v>
+        <v>6395324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122307304</v>
+        <v>122306231</v>
       </c>
       <c r="B7" t="n">
-        <v>96770</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,34 +1277,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340549</v>
+        <v>340201</v>
       </c>
       <c r="R7" t="n">
-        <v>6395257</v>
+        <v>6395464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122307224</v>
+        <v>122307101</v>
       </c>
       <c r="B8" t="n">
         <v>96770</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340498</v>
+        <v>340396</v>
       </c>
       <c r="R8" t="n">
-        <v>6395324</v>
+        <v>6395398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307101</v>
+        <v>122307133</v>
       </c>
       <c r="B9" t="n">
-        <v>96770</v>
+        <v>95006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122307133</v>
+        <v>122307304</v>
       </c>
       <c r="B10" t="n">
-        <v>95006</v>
+        <v>96770</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,21 +1588,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>535</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340396</v>
+        <v>340549</v>
       </c>
       <c r="R10" t="n">
-        <v>6395398</v>
+        <v>6395257</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122307224</v>
+        <v>122306231</v>
       </c>
       <c r="B6" t="n">
-        <v>96770</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,34 +1175,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340498</v>
+        <v>340201</v>
       </c>
       <c r="R6" t="n">
-        <v>6395324</v>
+        <v>6395464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122306231</v>
+        <v>122307133</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>95008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,39 +1282,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>535</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340201</v>
+        <v>340396</v>
       </c>
       <c r="R7" t="n">
-        <v>6395464</v>
+        <v>6395398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122307101</v>
+        <v>122307224</v>
       </c>
       <c r="B8" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340396</v>
+        <v>340498</v>
       </c>
       <c r="R8" t="n">
-        <v>6395398</v>
+        <v>6395324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307133</v>
+        <v>122307304</v>
       </c>
       <c r="B9" t="n">
-        <v>95006</v>
+        <v>96773</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>535</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340396</v>
+        <v>340549</v>
       </c>
       <c r="R9" t="n">
-        <v>6395398</v>
+        <v>6395257</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122307304</v>
+        <v>122307101</v>
       </c>
       <c r="B10" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340549</v>
+        <v>340396</v>
       </c>
       <c r="R10" t="n">
-        <v>6395257</v>
+        <v>6395398</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
         <v>122306971</v>
       </c>
       <c r="B11" t="n">
-        <v>95006</v>
+        <v>95008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122306231</v>
+        <v>122307133</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>95008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,39 +1175,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>535</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340201</v>
+        <v>340396</v>
       </c>
       <c r="R6" t="n">
-        <v>6395464</v>
+        <v>6395398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122307133</v>
+        <v>122306231</v>
       </c>
       <c r="B7" t="n">
-        <v>95008</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,34 +1277,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>535</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340396</v>
+        <v>340201</v>
       </c>
       <c r="R7" t="n">
-        <v>6395398</v>
+        <v>6395464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122307224</v>
+        <v>122307304</v>
       </c>
       <c r="B8" t="n">
         <v>96773</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340498</v>
+        <v>340549</v>
       </c>
       <c r="R8" t="n">
-        <v>6395324</v>
+        <v>6395257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307304</v>
+        <v>122307224</v>
       </c>
       <c r="B9" t="n">
         <v>96773</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340549</v>
+        <v>340498</v>
       </c>
       <c r="R9" t="n">
-        <v>6395257</v>
+        <v>6395324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122307133</v>
+        <v>122307224</v>
       </c>
       <c r="B6" t="n">
-        <v>95008</v>
+        <v>96774</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>535</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340396</v>
+        <v>340498</v>
       </c>
       <c r="R6" t="n">
-        <v>6395398</v>
+        <v>6395324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122306231</v>
+        <v>122307101</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>96774</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,39 +1277,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340201</v>
+        <v>340396</v>
       </c>
       <c r="R7" t="n">
-        <v>6395464</v>
+        <v>6395398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,7 +1366,7 @@
         <v>122307304</v>
       </c>
       <c r="B8" t="n">
-        <v>96773</v>
+        <v>96774</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307224</v>
+        <v>122307133</v>
       </c>
       <c r="B9" t="n">
-        <v>96773</v>
+        <v>95009</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1510,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340498</v>
+        <v>340396</v>
       </c>
       <c r="R9" t="n">
-        <v>6395324</v>
+        <v>6395398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122307101</v>
+        <v>122306231</v>
       </c>
       <c r="B10" t="n">
-        <v>96773</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,34 +1583,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340396</v>
+        <v>340201</v>
       </c>
       <c r="R10" t="n">
-        <v>6395398</v>
+        <v>6395464</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
         <v>122306971</v>
       </c>
       <c r="B11" t="n">
-        <v>95008</v>
+        <v>95009</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>122307224</v>
       </c>
       <c r="B6" t="n">
-        <v>96774</v>
+        <v>96777</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122307101</v>
+        <v>122307304</v>
       </c>
       <c r="B7" t="n">
-        <v>96774</v>
+        <v>96777</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340396</v>
+        <v>340549</v>
       </c>
       <c r="R7" t="n">
-        <v>6395398</v>
+        <v>6395257</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122307304</v>
+        <v>122307101</v>
       </c>
       <c r="B8" t="n">
-        <v>96774</v>
+        <v>96777</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340549</v>
+        <v>340396</v>
       </c>
       <c r="R8" t="n">
-        <v>6395257</v>
+        <v>6395398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307133</v>
+        <v>122306231</v>
       </c>
       <c r="B9" t="n">
-        <v>95009</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,34 +1481,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>535</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340396</v>
+        <v>340201</v>
       </c>
       <c r="R9" t="n">
-        <v>6395398</v>
+        <v>6395464</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122306231</v>
+        <v>122307133</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>95012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,39 +1588,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>535</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340201</v>
+        <v>340396</v>
       </c>
       <c r="R10" t="n">
-        <v>6395464</v>
+        <v>6395398</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
         <v>122306971</v>
       </c>
       <c r="B11" t="n">
-        <v>95009</v>
+        <v>95012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122307224</v>
+        <v>122307304</v>
       </c>
       <c r="B6" t="n">
         <v>96777</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340498</v>
+        <v>340549</v>
       </c>
       <c r="R6" t="n">
-        <v>6395324</v>
+        <v>6395257</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122307304</v>
+        <v>122307224</v>
       </c>
       <c r="B7" t="n">
         <v>96777</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340549</v>
+        <v>340498</v>
       </c>
       <c r="R7" t="n">
-        <v>6395257</v>
+        <v>6395324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122307101</v>
+        <v>122307133</v>
       </c>
       <c r="B8" t="n">
-        <v>96777</v>
+        <v>95012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,21 +1379,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122306231</v>
+        <v>122307101</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>96777</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,39 +1481,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340201</v>
+        <v>340396</v>
       </c>
       <c r="R9" t="n">
-        <v>6395464</v>
+        <v>6395398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122307133</v>
+        <v>122306231</v>
       </c>
       <c r="B10" t="n">
-        <v>95012</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,34 +1583,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>535</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340396</v>
+        <v>340201</v>
       </c>
       <c r="R10" t="n">
-        <v>6395398</v>
+        <v>6395464</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90772687</v>
+        <v>122306971</v>
       </c>
       <c r="B2" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härryda kommun, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>340418.9873265538</v>
+        <v>340311</v>
       </c>
       <c r="R2" t="n">
-        <v>6395381.852383995</v>
+        <v>6395441</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-11-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,38 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Dahlqvist, Jonas Mattsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>JSN0127 Härryda naturvårdsplan 2020</t>
-        </is>
-      </c>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90772688</v>
+        <v>122307133</v>
       </c>
       <c r="B3" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,38 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härryda kommun, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>340380.9401465154</v>
+        <v>340396</v>
       </c>
       <c r="R3" t="n">
-        <v>6395382.819723282</v>
+        <v>6395398</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-11-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,38 +851,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Dahlqvist, Jonas Mattsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>JSN0127 Härryda naturvårdsplan 2020</t>
-        </is>
-      </c>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>90772767</v>
       </c>
       <c r="B4" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>340323.9440095501</v>
+        <v>340324</v>
       </c>
       <c r="R4" t="n">
-        <v>6395365.797707821</v>
+        <v>6395366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,19 +941,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-11-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +959,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1041,12 +978,7 @@
         <v>90772686</v>
       </c>
       <c r="B5" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>340621.7244646656</v>
+        <v>340622</v>
       </c>
       <c r="R5" t="n">
-        <v>6395122.749929386</v>
+        <v>6395123</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,19 +1047,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-11-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1065,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ann-Sofie Lindén</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1159,15 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122307304</v>
+        <v>90772687</v>
       </c>
       <c r="B6" t="n">
-        <v>96777</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,16 +1110,20 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Härryda kommun, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340549</v>
+        <v>340419</v>
       </c>
       <c r="R6" t="n">
-        <v>6395257</v>
+        <v>6395382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,12 +1150,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-25</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-25</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,33 +1164,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Andreas Dahlqvist, Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>JSN0127 Härryda naturvårdsplan 2020</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122307224</v>
+        <v>90772688</v>
       </c>
       <c r="B7" t="n">
-        <v>96777</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,16 +1216,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Härryda kommun, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340498</v>
+        <v>340381</v>
       </c>
       <c r="R7" t="n">
-        <v>6395324</v>
+        <v>6395383</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,12 +1256,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-25</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-25</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,33 +1270,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Andreas Dahlqvist, Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>JSN0127 Härryda naturvårdsplan 2020</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122307133</v>
+        <v>122307101</v>
       </c>
       <c r="B8" t="n">
-        <v>95012</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,21 +1304,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>535</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1465,15 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307101</v>
+        <v>122307224</v>
       </c>
       <c r="B9" t="n">
-        <v>96777</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340396</v>
+        <v>340498</v>
       </c>
       <c r="R9" t="n">
-        <v>6395398</v>
+        <v>6395324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,15 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122306231</v>
+        <v>122307304</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,39 +1498,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Vg</t>
+          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340201</v>
+        <v>340549</v>
       </c>
       <c r="R10" t="n">
-        <v>6395464</v>
+        <v>6395257</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122306971</v>
+        <v>122307350</v>
       </c>
       <c r="B11" t="n">
-        <v>95012</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,34 +1595,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>535</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öst om Landvetter flygplats, Öst om Landvetter flygplats, Vg</t>
+          <t>Prästmossen, Härryda, Prästmossen, Härryda, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>340311</v>
+        <v>340565</v>
       </c>
       <c r="R11" t="n">
-        <v>6395441</v>
+        <v>6395253</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,6 +1683,108 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122306231</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öst om Landvetter flygplats, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>340201</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6395464</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52061-2024 artfynd.xlsx
+++ b/artfynd/A 52061-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122306971</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122307133</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
           <t>JSN0127 Härryda naturvårdsplan 2020</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90772767</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
           <t>JSN0127 Härryda naturvårdsplan 2020</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90772687</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
           <t>JSN0127 Härryda naturvårdsplan 2020</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90772688</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122307101</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122306231</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1489,6 +1529,11 @@
           <t>JSN0127 Härryda naturvårdsplan 2020</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90772686</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122307224</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,6 +1733,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122307304</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1785,8 +1840,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122307350</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>